--- a/npc/doc/NPC性能评估结果.xlsx
+++ b/npc/doc/NPC性能评估结果.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="62">
   <si>
     <t xml:space="preserve">commit</t>
   </si>
@@ -207,7 +207,10 @@
     <t xml:space="preserve">平均每次周期</t>
   </si>
   <si>
-    <t xml:space="preserve">多周期处理器，未添加</t>
+    <t xml:space="preserve">dd205ae4504fc2250f8684e2a33f90e3a2e8a0d7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">多周期处理器，根据综合结果插入寄存器优化频率</t>
   </si>
 </sst>
 </file>
@@ -288,7 +291,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -311,6 +314,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -336,7 +343,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:CR1048576"/>
-  <sheetFormatPr defaultColWidth="13.5859375" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.57421875" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -854,269 +861,278 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+    <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="B4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>10249068096</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>195179616</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>0.019</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="F4" s="0" t="n">
+        <v>727.908</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>13235.096</v>
+      </c>
+      <c r="H4" s="7" t="n">
         <v>195179616</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="K4" s="7" t="n">
         <v>8838413966</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="7" t="n">
         <v>86.24</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="7" t="n">
         <v>195179616</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="O4" s="7" t="n">
         <v>1215474512</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="P4" s="7" t="n">
         <v>11.86</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="R4" s="7" t="n">
         <v>195179616</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="S4" s="7" t="n">
         <v>8838413968</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="T4" s="7" t="n">
         <v>86.24</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="U4" s="7" t="n">
         <v>195179616</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="V4" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="W4" s="6" t="n">
+      <c r="W4" s="7" t="n">
         <v>1215474512</v>
       </c>
-      <c r="X4" s="6" t="n">
+      <c r="X4" s="7" t="n">
         <v>11.86</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="Z4" s="7" t="n">
         <v>195179616</v>
       </c>
-      <c r="AA4" s="6" t="n">
+      <c r="AA4" s="7" t="n">
         <v>9033593584</v>
       </c>
-      <c r="AB4" s="6" t="n">
+      <c r="AB4" s="7" t="n">
         <v>88.14</v>
       </c>
-      <c r="AC4" s="6" t="n">
+      <c r="AC4" s="7" t="n">
         <v>195179616</v>
       </c>
-      <c r="AD4" s="6" t="n">
+      <c r="AD4" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="AE4" s="6" t="n">
+      <c r="AE4" s="7" t="n">
         <v>1020294896</v>
       </c>
-      <c r="AF4" s="6" t="n">
+      <c r="AF4" s="7" t="n">
         <v>9.96</v>
       </c>
-      <c r="AH4" s="6" t="n">
+      <c r="AH4" s="7" t="n">
         <v>15597897</v>
       </c>
-      <c r="AI4" s="6" t="n">
+      <c r="AI4" s="7" t="n">
         <v>7154860</v>
       </c>
-      <c r="AJ4" s="6" t="n">
+      <c r="AJ4" s="7" t="n">
         <v>9251525958</v>
       </c>
-      <c r="AK4" s="6" t="n">
+      <c r="AK4" s="7" t="n">
         <v>90.27</v>
       </c>
-      <c r="AL4" s="6" t="n">
+      <c r="AL4" s="7" t="n">
         <v>624853786</v>
       </c>
-      <c r="AM4" s="6" t="n">
+      <c r="AM4" s="7" t="n">
         <v>6.1</v>
       </c>
-      <c r="AN4" s="6" t="n">
+      <c r="AN4" s="7" t="n">
         <v>15597897</v>
       </c>
-      <c r="AO4" s="6" t="n">
+      <c r="AO4" s="7" t="n">
         <v>0.15</v>
       </c>
-      <c r="AP4" s="6" t="n">
+      <c r="AP4" s="7" t="n">
         <v>154755980</v>
       </c>
-      <c r="AQ4" s="6" t="n">
+      <c r="AQ4" s="7" t="n">
         <v>1.51</v>
       </c>
-      <c r="AR4" s="6" t="n">
+      <c r="AR4" s="7" t="n">
         <v>7154860</v>
       </c>
-      <c r="AS4" s="6" t="n">
+      <c r="AS4" s="7" t="n">
         <v>0.07</v>
       </c>
-      <c r="AT4" s="6" t="n">
+      <c r="AT4" s="7" t="n">
         <v>195179615</v>
       </c>
-      <c r="AU4" s="6" t="n">
+      <c r="AU4" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="AW4" s="6" t="n">
+      <c r="AW4" s="7" t="n">
         <v>195179616</v>
       </c>
-      <c r="AX4" s="6" t="n">
+      <c r="AX4" s="7" t="n">
         <v>10053888480</v>
       </c>
-      <c r="AY4" s="6" t="n">
+      <c r="AY4" s="7" t="n">
         <v>98.1</v>
       </c>
-      <c r="AZ4" s="6" t="n">
+      <c r="AZ4" s="7" t="n">
         <v>195179616</v>
       </c>
-      <c r="BA4" s="6" t="n">
+      <c r="BA4" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="BC4" s="6" t="n">
+      <c r="BC4" s="7" t="n">
         <v>1577524</v>
       </c>
-      <c r="BD4" s="6" t="n">
+      <c r="BD4" s="7" t="n">
         <v>1928723</v>
       </c>
-      <c r="BE4" s="6" t="n">
+      <c r="BE4" s="7" t="n">
         <v>2032838</v>
       </c>
-      <c r="BF4" s="6" t="n">
+      <c r="BF4" s="7" t="n">
         <v>88301344</v>
       </c>
-      <c r="BG4" s="6" t="n">
+      <c r="BG4" s="7" t="n">
         <v>52598631</v>
       </c>
-      <c r="BH4" s="6" t="n">
+      <c r="BH4" s="7" t="n">
         <v>25987797</v>
       </c>
-      <c r="BI4" s="6" t="n">
+      <c r="BI4" s="7" t="n">
         <v>15597897</v>
       </c>
-      <c r="BJ4" s="6" t="n">
+      <c r="BJ4" s="7" t="n">
         <v>7154860</v>
       </c>
-      <c r="BK4" s="6" t="n">
+      <c r="BK4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="BL4" s="6" t="n">
+      <c r="BL4" s="7" t="n">
         <v>10249068096</v>
       </c>
-      <c r="BM4" s="6" t="n">
+      <c r="BM4" s="7" t="n">
         <v>89933678</v>
       </c>
-      <c r="BN4" s="6" t="n">
+      <c r="BN4" s="7" t="n">
         <v>0.88</v>
       </c>
-      <c r="BO4" s="6" t="n">
+      <c r="BO4" s="7" t="n">
         <v>57.01</v>
       </c>
-      <c r="BP4" s="6" t="n">
+      <c r="BP4" s="7" t="n">
         <v>90409244</v>
       </c>
-      <c r="BQ4" s="6" t="n">
+      <c r="BQ4" s="7" t="n">
         <v>0.88</v>
       </c>
-      <c r="BR4" s="6" t="n">
+      <c r="BR4" s="7" t="n">
         <v>46.88</v>
       </c>
-      <c r="BS4" s="6" t="n">
+      <c r="BS4" s="7" t="n">
         <v>97021159</v>
       </c>
-      <c r="BT4" s="6" t="n">
+      <c r="BT4" s="7" t="n">
         <v>0.95</v>
       </c>
-      <c r="BU4" s="6" t="n">
+      <c r="BU4" s="7" t="n">
         <v>47.73</v>
       </c>
-      <c r="BV4" s="6" t="n">
+      <c r="BV4" s="7" t="n">
         <v>4259224237</v>
       </c>
-      <c r="BW4" s="6" t="n">
+      <c r="BW4" s="7" t="n">
         <v>41.56</v>
       </c>
-      <c r="BX4" s="6" t="n">
+      <c r="BX4" s="7" t="n">
         <v>48.24</v>
       </c>
-      <c r="BY4" s="6" t="n">
+      <c r="BY4" s="7" t="n">
         <v>2495938854</v>
       </c>
-      <c r="BZ4" s="6" t="n">
+      <c r="BZ4" s="7" t="n">
         <v>24.35</v>
       </c>
-      <c r="CA4" s="6" t="n">
+      <c r="CA4" s="7" t="n">
         <v>47.45</v>
       </c>
-      <c r="CB4" s="6" t="n">
+      <c r="CB4" s="7" t="n">
         <v>1263483030</v>
       </c>
-      <c r="CC4" s="6" t="n">
+      <c r="CC4" s="7" t="n">
         <v>12.33</v>
       </c>
-      <c r="CD4" s="6" t="n">
+      <c r="CD4" s="7" t="n">
         <v>48.62</v>
       </c>
-      <c r="CE4" s="6" t="n">
+      <c r="CE4" s="7" t="n">
         <v>1439103046</v>
       </c>
-      <c r="CF4" s="6" t="n">
+      <c r="CF4" s="7" t="n">
         <v>14.04</v>
       </c>
-      <c r="CG4" s="6" t="n">
+      <c r="CG4" s="7" t="n">
         <v>92.26</v>
       </c>
-      <c r="CH4" s="6" t="n">
+      <c r="CH4" s="7" t="n">
         <v>513954758</v>
       </c>
-      <c r="CI4" s="6" t="n">
+      <c r="CI4" s="7" t="n">
         <v>5.01</v>
       </c>
-      <c r="CJ4" s="6" t="n">
+      <c r="CJ4" s="7" t="n">
         <v>71.83</v>
       </c>
-      <c r="CK4" s="6" t="n">
+      <c r="CK4" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="CL4" s="6" t="n">
+      <c r="CL4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="CM4" s="6" t="n">
+      <c r="CM4" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="CN4" s="6" t="n">
+      <c r="CN4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="CO4" s="6" t="n">
+      <c r="CO4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="CP4" s="6" t="n">
+      <c r="CP4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="CQ4" s="6" t="n">
+      <c r="CQ4" s="7" t="n">
         <v>40.06</v>
       </c>
-      <c r="CR4" s="6" t="n">
+      <c r="CR4" s="7" t="n">
         <v>21.63</v>
       </c>
     </row>

--- a/npc/doc/NPC性能评估结果.xlsx
+++ b/npc/doc/NPC性能评估结果.xlsx
@@ -207,7 +207,7 @@
     <t xml:space="preserve">平均每次周期</t>
   </si>
   <si>
-    <t xml:space="preserve">dd205ae4504fc2250f8684e2a33f90e3a2e8a0d7</t>
+    <t xml:space="preserve">b8b0f733b8c36dc762e98e26ce5d507581928a93</t>
   </si>
   <si>
     <t xml:space="preserve">多周期处理器，根据综合结果插入寄存器优化频率</t>
@@ -343,7 +343,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:CR1048576"/>
-  <sheetFormatPr defaultColWidth="13.57421875" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.55859375" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -862,7 +862,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -877,10 +877,10 @@
       <c r="E4" s="7" t="n">
         <v>0.019</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="6" t="n">
         <v>727.908</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="6" t="n">
         <v>13235.096</v>
       </c>
       <c r="H4" s="7" t="n">

--- a/npc/doc/NPC性能评估结果.xlsx
+++ b/npc/doc/NPC性能评估结果.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
   <si>
     <t xml:space="preserve">commit</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t xml:space="preserve">多周期处理器，根据综合结果插入寄存器优化频率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">添加了一个 块大小为4B, 共16个cache块的icache</t>
   </si>
 </sst>
 </file>
@@ -220,7 +223,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
@@ -247,6 +250,11 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -316,11 +324,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -343,7 +351,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:CR1048576"/>
-  <sheetFormatPr defaultColWidth="13.55859375" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.55078125" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -861,20 +869,20 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="6" t="n">
         <v>10249068096</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="6" t="n">
         <v>195179616</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="6" t="n">
         <v>0.019</v>
       </c>
       <c r="F4" s="6" t="n">
@@ -883,257 +891,529 @@
       <c r="G4" s="6" t="n">
         <v>13235.096</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="6" t="n">
         <v>195179616</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="6" t="n">
         <v>8838413966</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="6" t="n">
         <v>86.24</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="6" t="n">
         <v>195179616</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="N4" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="O4" s="7" t="n">
+      <c r="O4" s="6" t="n">
         <v>1215474512</v>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="P4" s="6" t="n">
         <v>11.86</v>
       </c>
-      <c r="R4" s="7" t="n">
+      <c r="R4" s="6" t="n">
         <v>195179616</v>
       </c>
-      <c r="S4" s="7" t="n">
+      <c r="S4" s="6" t="n">
         <v>8838413968</v>
       </c>
-      <c r="T4" s="7" t="n">
+      <c r="T4" s="6" t="n">
         <v>86.24</v>
       </c>
-      <c r="U4" s="7" t="n">
+      <c r="U4" s="6" t="n">
         <v>195179616</v>
       </c>
-      <c r="V4" s="7" t="n">
+      <c r="V4" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="W4" s="7" t="n">
+      <c r="W4" s="6" t="n">
         <v>1215474512</v>
       </c>
-      <c r="X4" s="7" t="n">
+      <c r="X4" s="6" t="n">
         <v>11.86</v>
       </c>
-      <c r="Z4" s="7" t="n">
+      <c r="Z4" s="6" t="n">
         <v>195179616</v>
       </c>
-      <c r="AA4" s="7" t="n">
+      <c r="AA4" s="6" t="n">
         <v>9033593584</v>
       </c>
-      <c r="AB4" s="7" t="n">
+      <c r="AB4" s="6" t="n">
         <v>88.14</v>
       </c>
-      <c r="AC4" s="7" t="n">
+      <c r="AC4" s="6" t="n">
         <v>195179616</v>
       </c>
-      <c r="AD4" s="7" t="n">
+      <c r="AD4" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="AE4" s="7" t="n">
+      <c r="AE4" s="6" t="n">
         <v>1020294896</v>
       </c>
-      <c r="AF4" s="7" t="n">
+      <c r="AF4" s="6" t="n">
         <v>9.96</v>
       </c>
-      <c r="AH4" s="7" t="n">
+      <c r="AH4" s="6" t="n">
         <v>15597897</v>
       </c>
-      <c r="AI4" s="7" t="n">
+      <c r="AI4" s="6" t="n">
         <v>7154860</v>
       </c>
-      <c r="AJ4" s="7" t="n">
+      <c r="AJ4" s="6" t="n">
         <v>9251525958</v>
       </c>
-      <c r="AK4" s="7" t="n">
+      <c r="AK4" s="6" t="n">
         <v>90.27</v>
       </c>
-      <c r="AL4" s="7" t="n">
+      <c r="AL4" s="6" t="n">
         <v>624853786</v>
       </c>
-      <c r="AM4" s="7" t="n">
+      <c r="AM4" s="6" t="n">
         <v>6.1</v>
       </c>
-      <c r="AN4" s="7" t="n">
+      <c r="AN4" s="6" t="n">
         <v>15597897</v>
       </c>
-      <c r="AO4" s="7" t="n">
+      <c r="AO4" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="AP4" s="7" t="n">
+      <c r="AP4" s="6" t="n">
         <v>154755980</v>
       </c>
-      <c r="AQ4" s="7" t="n">
+      <c r="AQ4" s="6" t="n">
         <v>1.51</v>
       </c>
-      <c r="AR4" s="7" t="n">
+      <c r="AR4" s="6" t="n">
         <v>7154860</v>
       </c>
-      <c r="AS4" s="7" t="n">
+      <c r="AS4" s="6" t="n">
         <v>0.07</v>
       </c>
-      <c r="AT4" s="7" t="n">
+      <c r="AT4" s="6" t="n">
         <v>195179615</v>
       </c>
-      <c r="AU4" s="7" t="n">
+      <c r="AU4" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="AW4" s="7" t="n">
+      <c r="AW4" s="6" t="n">
         <v>195179616</v>
       </c>
-      <c r="AX4" s="7" t="n">
+      <c r="AX4" s="6" t="n">
         <v>10053888480</v>
       </c>
-      <c r="AY4" s="7" t="n">
+      <c r="AY4" s="6" t="n">
         <v>98.1</v>
       </c>
-      <c r="AZ4" s="7" t="n">
+      <c r="AZ4" s="6" t="n">
         <v>195179616</v>
       </c>
-      <c r="BA4" s="7" t="n">
+      <c r="BA4" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="BC4" s="7" t="n">
+      <c r="BC4" s="6" t="n">
         <v>1577524</v>
       </c>
-      <c r="BD4" s="7" t="n">
+      <c r="BD4" s="6" t="n">
         <v>1928723</v>
       </c>
-      <c r="BE4" s="7" t="n">
+      <c r="BE4" s="6" t="n">
         <v>2032838</v>
       </c>
-      <c r="BF4" s="7" t="n">
+      <c r="BF4" s="6" t="n">
         <v>88301344</v>
       </c>
-      <c r="BG4" s="7" t="n">
+      <c r="BG4" s="6" t="n">
         <v>52598631</v>
       </c>
-      <c r="BH4" s="7" t="n">
+      <c r="BH4" s="6" t="n">
         <v>25987797</v>
       </c>
-      <c r="BI4" s="7" t="n">
+      <c r="BI4" s="6" t="n">
         <v>15597897</v>
       </c>
-      <c r="BJ4" s="7" t="n">
+      <c r="BJ4" s="6" t="n">
         <v>7154860</v>
       </c>
-      <c r="BK4" s="7" t="n">
+      <c r="BK4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="BL4" s="7" t="n">
+      <c r="BL4" s="6" t="n">
         <v>10249068096</v>
       </c>
-      <c r="BM4" s="7" t="n">
+      <c r="BM4" s="6" t="n">
         <v>89933678</v>
       </c>
-      <c r="BN4" s="7" t="n">
+      <c r="BN4" s="6" t="n">
         <v>0.88</v>
       </c>
-      <c r="BO4" s="7" t="n">
+      <c r="BO4" s="6" t="n">
         <v>57.01</v>
       </c>
-      <c r="BP4" s="7" t="n">
+      <c r="BP4" s="6" t="n">
         <v>90409244</v>
       </c>
-      <c r="BQ4" s="7" t="n">
+      <c r="BQ4" s="6" t="n">
         <v>0.88</v>
       </c>
-      <c r="BR4" s="7" t="n">
+      <c r="BR4" s="6" t="n">
         <v>46.88</v>
       </c>
-      <c r="BS4" s="7" t="n">
+      <c r="BS4" s="6" t="n">
         <v>97021159</v>
       </c>
-      <c r="BT4" s="7" t="n">
+      <c r="BT4" s="6" t="n">
         <v>0.95</v>
       </c>
-      <c r="BU4" s="7" t="n">
+      <c r="BU4" s="6" t="n">
         <v>47.73</v>
       </c>
-      <c r="BV4" s="7" t="n">
+      <c r="BV4" s="6" t="n">
         <v>4259224237</v>
       </c>
-      <c r="BW4" s="7" t="n">
+      <c r="BW4" s="6" t="n">
         <v>41.56</v>
       </c>
-      <c r="BX4" s="7" t="n">
+      <c r="BX4" s="6" t="n">
         <v>48.24</v>
       </c>
-      <c r="BY4" s="7" t="n">
+      <c r="BY4" s="6" t="n">
         <v>2495938854</v>
       </c>
-      <c r="BZ4" s="7" t="n">
+      <c r="BZ4" s="6" t="n">
         <v>24.35</v>
       </c>
-      <c r="CA4" s="7" t="n">
+      <c r="CA4" s="6" t="n">
         <v>47.45</v>
       </c>
-      <c r="CB4" s="7" t="n">
+      <c r="CB4" s="6" t="n">
         <v>1263483030</v>
       </c>
-      <c r="CC4" s="7" t="n">
+      <c r="CC4" s="6" t="n">
         <v>12.33</v>
       </c>
-      <c r="CD4" s="7" t="n">
+      <c r="CD4" s="6" t="n">
         <v>48.62</v>
       </c>
-      <c r="CE4" s="7" t="n">
+      <c r="CE4" s="6" t="n">
         <v>1439103046</v>
       </c>
-      <c r="CF4" s="7" t="n">
+      <c r="CF4" s="6" t="n">
         <v>14.04</v>
       </c>
-      <c r="CG4" s="7" t="n">
+      <c r="CG4" s="6" t="n">
         <v>92.26</v>
       </c>
-      <c r="CH4" s="7" t="n">
+      <c r="CH4" s="6" t="n">
         <v>513954758</v>
       </c>
-      <c r="CI4" s="7" t="n">
+      <c r="CI4" s="6" t="n">
         <v>5.01</v>
       </c>
-      <c r="CJ4" s="7" t="n">
+      <c r="CJ4" s="6" t="n">
         <v>71.83</v>
       </c>
-      <c r="CK4" s="7" t="n">
+      <c r="CK4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="CL4" s="7" t="n">
+      <c r="CL4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="CM4" s="7" t="n">
+      <c r="CM4" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="CN4" s="7" t="n">
+      <c r="CN4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="CO4" s="7" t="n">
+      <c r="CO4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="CP4" s="7" t="n">
+      <c r="CP4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="CQ4" s="7" t="n">
+      <c r="CQ4" s="6" t="n">
         <v>40.06</v>
       </c>
-      <c r="CR4" s="7" t="n">
+      <c r="CR4" s="6" t="n">
         <v>21.63</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>4751195380</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>735.075</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>37452.268</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>195176351</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>2992788185</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>1368054495</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="R5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="S5" s="0" t="n">
+        <v>3383140885</v>
+      </c>
+      <c r="T5" s="0" t="n">
+        <v>71.21</v>
+      </c>
+      <c r="U5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="V5" s="0" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="W5" s="0" t="n">
+        <v>1172878146</v>
+      </c>
+      <c r="X5" s="0" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="Z5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="AA5" s="0" t="n">
+        <v>3578317234</v>
+      </c>
+      <c r="AB5" s="0" t="n">
+        <v>75.31</v>
+      </c>
+      <c r="AC5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="AD5" s="0" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AE5" s="0" t="n">
+        <v>977701797</v>
+      </c>
+      <c r="AF5" s="0" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="AH5" s="0" t="n">
+        <v>15597770</v>
+      </c>
+      <c r="AI5" s="0" t="n">
+        <v>7154738</v>
+      </c>
+      <c r="AJ5" s="0" t="n">
+        <v>3773493583</v>
+      </c>
+      <c r="AK5" s="0" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="AL5" s="0" t="n">
+        <v>614939759</v>
+      </c>
+      <c r="AM5" s="0" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="AN5" s="0" t="n">
+        <v>15597770</v>
+      </c>
+      <c r="AO5" s="0" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP5" s="0" t="n">
+        <v>144833181</v>
+      </c>
+      <c r="AQ5" s="0" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AR5" s="0" t="n">
+        <v>7154738</v>
+      </c>
+      <c r="AS5" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AT5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="AU5" s="0" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AW5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="AX5" s="0" t="n">
+        <v>4556019031</v>
+      </c>
+      <c r="AY5" s="0" t="n">
+        <v>95.89</v>
+      </c>
+      <c r="AZ5" s="0" t="n">
+        <v>195176349</v>
+      </c>
+      <c r="BA5" s="0" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BC5" s="0" t="n">
+        <v>1577508</v>
+      </c>
+      <c r="BD5" s="0" t="n">
+        <v>1928718</v>
+      </c>
+      <c r="BE5" s="0" t="n">
+        <v>2032838</v>
+      </c>
+      <c r="BF5" s="0" t="n">
+        <v>88300180</v>
+      </c>
+      <c r="BG5" s="0" t="n">
+        <v>52598628</v>
+      </c>
+      <c r="BH5" s="0" t="n">
+        <v>25985967</v>
+      </c>
+      <c r="BI5" s="0" t="n">
+        <v>15597770</v>
+      </c>
+      <c r="BJ5" s="0" t="n">
+        <v>7154738</v>
+      </c>
+      <c r="BK5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL5" s="0" t="n">
+        <v>4751195379</v>
+      </c>
+      <c r="BM5" s="0" t="n">
+        <v>99070774</v>
+      </c>
+      <c r="BN5" s="0" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BO5" s="0" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="BP5" s="0" t="n">
+        <v>100609959</v>
+      </c>
+      <c r="BQ5" s="0" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BR5" s="0" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="BS5" s="0" t="n">
+        <v>87228483</v>
+      </c>
+      <c r="BT5" s="0" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BU5" s="0" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="BV5" s="0" t="n">
+        <v>1505557846</v>
+      </c>
+      <c r="BW5" s="0" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="BX5" s="0" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="BY5" s="0" t="n">
+        <v>674349616</v>
+      </c>
+      <c r="BZ5" s="0" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="CA5" s="0" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="CB5" s="0" t="n">
+        <v>667309208</v>
+      </c>
+      <c r="CC5" s="0" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="CD5" s="0" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="CE5" s="0" t="n">
+        <v>1200448322</v>
+      </c>
+      <c r="CF5" s="0" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="CG5" s="0" t="n">
+        <v>76.96</v>
+      </c>
+      <c r="CH5" s="0" t="n">
+        <v>416621071</v>
+      </c>
+      <c r="CI5" s="0" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="CJ5" s="0" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="CK5" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="CL5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="CN5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" s="0" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="CR5" s="0" t="n">
+        <v>20.24</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/npc/doc/NPC性能评估结果.xlsx
+++ b/npc/doc/NPC性能评估结果.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="64">
   <si>
     <t xml:space="preserve">commit</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t xml:space="preserve">多周期处理器，根据综合结果插入寄存器优化频率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8505988f07420d7b6b33acfe3979442aa9c6f636</t>
   </si>
   <si>
     <t xml:space="preserve">添加了一个 块大小为4B, 共16个cache块的icache</t>
@@ -223,7 +226,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
@@ -250,11 +253,6 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Microsoft YaHei"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -328,7 +326,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -351,7 +349,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:CR1048576"/>
-  <sheetFormatPr defaultColWidth="13.55078125" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.53515625" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1145,8 +1143,11 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>62</v>
+      </c>
       <c r="B5" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>4751195380</v>
